--- a/Stats Sheet/Round Gaps/Discovery.xlsx
+++ b/Stats Sheet/Round Gaps/Discovery.xlsx
@@ -70,6 +70,9 @@
     <x:t>LimitDTW</x:t>
   </x:si>
   <x:si>
+    <x:t>lolmcgeeksFTW</x:t>
+  </x:si>
+  <x:si>
     <x:t>numdegased</x:t>
   </x:si>
   <x:si>
@@ -83,9 +86,6 @@
   </x:si>
   <x:si>
     <x:t>Skymeagle</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TheBestOtaku</x:t>
   </x:si>
   <x:si>
     <x:t>TheRCPanda</x:t>
@@ -821,16 +821,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D16" s="0">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E16" s="0" t="s">
         <x:v>5</x:v>
-      </x:c>
-      <x:c r="F16" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="H16" s="0" t="s">
-        <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:8">
@@ -844,13 +838,16 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D17" s="0">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="E17" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
+      <x:c r="F17" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
       <x:c r="H17" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:8">
@@ -858,16 +855,19 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C18" s="0" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D18" s="0">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E18" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="H18" s="0" t="s">
         <x:v>22</x:v>
-      </x:c>
-      <x:c r="C18" s="0" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E18" s="0" t="s">
-        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:8">
